--- a/results/final_N33_v5/Trend_Method_Comparison/Tables/Table_M4_Station_Disagreement_Inventory.xlsx
+++ b/results/final_N33_v5/Trend_Method_Comparison/Tables/Table_M4_Station_Disagreement_Inventory.xlsx
@@ -467,9 +467,9 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
@@ -629,14 +629,14 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>33.03768069475208</v>
+        <v>12.48</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1.029127931652926</v>
+        <v>2.725068</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>k=1(ρ=+0.582); k=2(ρ=+0.361); k=9(ρ=−0.432); k=10(ρ=−0.351)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
@@ -732,14 +732,14 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>32.94192253017283</v>
+        <v>20.27</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.032119481455827</v>
+        <v>1.677263</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>k=1(ρ=+0.360)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
@@ -835,14 +835,14 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>32.90392625434833</v>
+        <v>19.92</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1.033311336075184</v>
+        <v>1.706922</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>k=1(ρ=+0.376)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
@@ -938,14 +938,14 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>31.9728189685143</v>
+        <v>33</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.032126695881812</v>
+        <v>1</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>k=6(ρ=+0.384); k=10(ρ=−0.479)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
